--- a/results/Int Task Remove ACC -1.0/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_10_permute.xlsx
@@ -440,197 +440,197 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6783011265275491</v>
+        <v>0.6618427523316534</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6794196947602114</v>
+        <v>0.6607622040484495</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6749969441909781</v>
+        <v>0.668502639366211</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6737643161099409</v>
+        <v>0.685305680393645</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6737643161099409</v>
+        <v>0.6774536725139217</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6762540898095165</v>
+        <v>0.6776952946226289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6759364278018927</v>
+        <v>0.6758518600638451</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6724666632555309</v>
+        <v>0.6752545559980556</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6649163276850611</v>
+        <v>0.6811000343956178</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6646231832149385</v>
+        <v>0.6762810946334308</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6646231832149385</v>
+        <v>0.6666002205867723</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6546395708791349</v>
+        <v>0.6764882500589842</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6540422668133454</v>
+        <v>0.6764882500589842</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6438120577960085</v>
+        <v>0.6764882500589842</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6393487999909037</v>
+        <v>0.6758909459931948</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6265858227517063</v>
+        <v>0.6682720323830478</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6228499185591363</v>
+        <v>0.6900816256335474</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6413258373627373</v>
+        <v>0.6636556288002183</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6384153569327069</v>
+        <v>0.6631858869947611</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6404488912387823</v>
+        <v>0.6646601371845056</v>
       </c>
     </row>
     <row r="22">
@@ -640,607 +640,607 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6407800556583634</v>
+        <v>0.6628842146855075</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6556010847411374</v>
+        <v>0.6564609751868307</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6719159069783307</v>
+        <v>0.6303991881497147</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6836804163859587</v>
+        <v>0.5945463758105001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6747833928860766</v>
+        <v>0.5982147679432842</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6775638237693618</v>
+        <v>0.6337474309884619</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7099248413111268</v>
+        <v>0.65398292726606</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6974820133659665</v>
+        <v>0.6745684202746532</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6793333503890115</v>
+        <v>0.6746444601735699</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6790537083308461</v>
+        <v>0.7045672263771749</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6732892444050269</v>
+        <v>0.7059139143065871</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6446982424123551</v>
+        <v>0.6822178919750191</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6961008587534004</v>
+        <v>0.6741462922376766</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7579234285324441</v>
+        <v>0.6850793373300472</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7407426752968398</v>
+        <v>0.6840798035185864</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7205679398730489</v>
+        <v>0.6767746433231283</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7145543919792831</v>
+        <v>0.6774700175389226</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7142502323836163</v>
+        <v>0.6892395015193766</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7236575049248271</v>
+        <v>0.6855906523512674</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7317291046621697</v>
+        <v>0.6957092888066426</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7251072375770704</v>
+        <v>0.6939038741973171</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7065368018897692</v>
+        <v>0.6448034190949689</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7065368018897692</v>
+        <v>0.6654049018019323</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6795440590808695</v>
+        <v>0.6654049018019323</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6543492690220558</v>
+        <v>0.6774590024133784</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6713043898473232</v>
+        <v>0.6805620698771139</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6767181463888865</v>
+        <v>0.6007450488787314</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6813309967054115</v>
+        <v>0.5892331767053547</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6872905349513487</v>
+        <v>0.6476673517364102</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6277488068131749</v>
+        <v>0.608992179971517</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6266302385805128</v>
+        <v>0.616043281626202</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6355787844418104</v>
+        <v>0.6141238071685016</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6343681866118611</v>
+        <v>0.5966090469002726</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6276947971653463</v>
+        <v>0.6070883398855564</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6276947971653463</v>
+        <v>0.6070883398855564</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6231199667982796</v>
+        <v>0.611435050555873</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5977595945296754</v>
+        <v>0.5925899473832326</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5939256201871008</v>
+        <v>0.5870265983302491</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5977130467410863</v>
+        <v>0.5850691039230902</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5825878580626455</v>
+        <v>0.5857619908524713</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5770145598640094</v>
+        <v>0.570065436952264</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5721085650773617</v>
+        <v>0.5624635790203787</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6265001890337674</v>
+        <v>0.5632069223312838</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6272495728973901</v>
+        <v>0.5632879368030268</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6298203610687088</v>
+        <v>0.5962036192149271</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.634118036664023</v>
+        <v>0.5523307294997853</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6325272393394904</v>
+        <v>0.570882688202303</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6372051144293881</v>
+        <v>0.570882688202303</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6354132022320198</v>
+        <v>0.5460627677386161</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6893020390063362</v>
+        <v>0.5395315089442819</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6892640190568778</v>
+        <v>0.5297685544459889</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6776736196981714</v>
+        <v>0.514287683810466</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6776736196981714</v>
+        <v>0.507942971497119</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6907492843721663</v>
+        <v>0.5145108289343897</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6870673898274249</v>
+        <v>0.5221457322429069</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6799857300825211</v>
+        <v>0.5182577482525036</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6866150590268598</v>
+        <v>0.5196939784927898</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6385621068310834</v>
+        <v>0.523342827660899</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6385621068310834</v>
+        <v>0.5144728089849313</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6032550761962426</v>
+        <v>0.5141931669267658</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6022530550983687</v>
+        <v>0.5207659989368627</v>
       </c>
     </row>
     <row r="83">
@@ -1250,77 +1250,77 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6266295279272518</v>
+        <v>0.5036623515800664</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6160191194153313</v>
+        <v>0.5039800135876903</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5554071474662369</v>
+        <v>0.5048189397621869</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5435911156971935</v>
+        <v>0.5047318847377263</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5297522094209881</v>
+        <v>0.5044142227301024</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5331668983396297</v>
+        <v>0.5044142227301024</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4931986929665225</v>
+        <v>0.4974011410248757</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4931986929665225</v>
+        <v>0.4979224051917485</v>
       </c>
     </row>
   </sheetData>
